--- a/Skin Care.xlsx
+++ b/Skin Care.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\r.gill\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Boutiqaat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0994531-82F4-4B5E-AE90-3A801AF48B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{947B4B3A-6327-40C3-B776-513A0963BCC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -20,11 +20,16 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$J$101</definedName>
   </definedNames>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="402">
   <si>
     <t>Product Name</t>
   </si>
@@ -1620,7 +1625,7 @@
   <dimension ref="A1:J101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="55.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.5703125" customWidth="1"/>
